--- a/SCD Product Demo.xlsx
+++ b/SCD Product Demo.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\repos\sml\sml-salesinsights-databricks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25133852-2CA0-4396-B122-61AE3BE8E886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{024CFD76-D2E7-42B6-A377-D9AB01AE33AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{14D1C86D-1753-448B-A066-1B2874455ACA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{1B20A090-574D-47C0-A988-C71E03C9C9E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="64" r:id="rId2"/>
+    <pivotCache cacheId="203" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{8F85427D-831D-47A0-8B33-19C16539A795}" odcFile="C:\Mac\Home\Documents\Meine Datenquellen\https___dev.atscale-se-demo.com_engine_xmla_wvqlrjdoom70pylyfa2snq Sales Insights - Databricks Sales Product SCD.odc" keepAlive="1" name="https___dev.atscale-se-demo.com_engine_xmla_wvqlrjdoom70pylyfa2snq Sales Insights - Databricks Sales Product SCD" type="5" refreshedVersion="8" background="1">
+  <connection id="1" xr16:uid="{7022BF1B-E819-475E-80BD-22D2244235D8}" odcFile="C:\Mac\Home\Documents\Meine Datenquellen\https___dev.atscale-se-demo.com_engine_xmla_wvqlrjdoom70pylyfa2snq Sales Insights - Databricks Sales Product SCD.odc" keepAlive="1" name="https___dev.atscale-se-demo.com_engine_xmla_wvqlrjdoom70pylyfa2snq Sales Insights - Databricks Sales Product SCD" type="5" refreshedVersion="8" background="1">
     <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=Sales Insights - Databricks;Data Source=https://dev.atscale-se-demo.com/engine/xmla/wvqlrjdoom70pylyfa2snq;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="Sales Product SCD" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
   </connection>
@@ -51,48 +51,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>Sales Amount (SCD)</t>
   </si>
   <si>
-    <t>33.6442</t>
-  </si>
-  <si>
-    <t>34.99</t>
+    <t>2049.0981</t>
+  </si>
+  <si>
+    <t>2294.99</t>
   </si>
   <si>
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Sport-100 Helmet, Black</t>
-  </si>
-  <si>
-    <t>Sport-100 Helmet, Blue</t>
-  </si>
-  <si>
-    <t>Sport-100 Helmet, Red</t>
+    <t>99991231</t>
+  </si>
+  <si>
+    <t>20070630</t>
+  </si>
+  <si>
+    <t>20070701</t>
+  </si>
+  <si>
+    <t>20060701</t>
+  </si>
+  <si>
+    <t>product_scd effective-start</t>
+  </si>
+  <si>
+    <t>product_scd effective-end</t>
+  </si>
+  <si>
+    <t>List Price</t>
   </si>
   <si>
     <t>Product</t>
   </si>
   <si>
-    <t>List Price</t>
-  </si>
-  <si>
-    <t>product_scd effective-end</t>
-  </si>
-  <si>
-    <t>99991231</t>
-  </si>
-  <si>
-    <t>20070701</t>
-  </si>
-  <si>
-    <t>20060701</t>
-  </si>
-  <si>
-    <t>product_scd effective-start</t>
+    <t>Mountain-200 Black, 46</t>
+  </si>
+  <si>
+    <t>ReportIng Year</t>
+  </si>
+  <si>
+    <t>Reporting Calendar 2006</t>
+  </si>
+  <si>
+    <t>Reporting Calendar 2007</t>
+  </si>
+  <si>
+    <t>Reporting Calendar 2008</t>
   </si>
 </sst>
 </file>
@@ -153,73 +162,121 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="marco" refreshedDate="46303.499017592592" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1219A546-FF43-450E-AE3D-7E0A214A340E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="marco" refreshedDate="46303.523644097222" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{804BE516-455E-47A4-8A14-E7489116472E}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="10">
-    <cacheField name="[Measures].[salesamount_scd]" caption="Sales Amount (SCD)" numFmtId="0" hierarchy="26" level="32767"/>
-    <cacheField name="[Product SCD Dimension].[product_scd_list_price].[product_scd_list_price]" caption="List Price" numFmtId="0" hierarchy="19" level="1">
+  <cacheFields count="26">
+    <cacheField name="[Measures].[salesamount_scd]" caption="Sales Amount (SCD)" numFmtId="0" hierarchy="29" level="32767"/>
+    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd]" caption="Product" numFmtId="0" hierarchy="15" level="1" mappingCount="5">
       <sharedItems count="2">
-        <s v="[Product SCD Dimension].[product_scd_list_price].[product_scd_list_price].&amp;[33.6442]" c="33.6442"/>
-        <s v="[Product SCD Dimension].[product_scd_list_price].[product_scd_list_price].&amp;[34.99]" c="34.99"/>
+        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Mountain-200 Black, 46]&amp;[20060701]" c="Mountain-200 Black, 46"/>
+        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Mountain-200 Black, 46]&amp;[20070701]" c="Mountain-200 Black, 46"/>
       </sharedItems>
-    </cacheField>
-    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd]" caption="Product" numFmtId="0" hierarchy="12" level="1" mappingCount="5">
-      <sharedItems count="6">
-        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Black]&amp;[20060701]" c="Sport-100 Helmet, Black"/>
-        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Black]&amp;[20070701]" c="Sport-100 Helmet, Black"/>
-        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Blue]&amp;[20060701]" c="Sport-100 Helmet, Blue"/>
-        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Blue]&amp;[20070701]" c="Sport-100 Helmet, Blue"/>
-        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Red]&amp;[20060701]" c="Sport-100 Helmet, Red"/>
-        <s v="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Red]&amp;[20070701]" c="Sport-100 Helmet, Red"/>
-      </sharedItems>
+      <mpMap v="2"/>
       <mpMap v="3"/>
       <mpMap v="4"/>
       <mpMap v="5"/>
       <mpMap v="6"/>
-      <mpMap v="7"/>
-    </cacheField>
-    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[levelScdEffectiveEnd_product_scd]" caption="product_scd effective-end" propertyName="levelScdEffectiveEnd_product_scd" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20070701" maxValue="99991231" count="2">
-        <n v="20070701"/>
+    </cacheField>
+    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[levelScdEffectiveEnd_product_scd]" caption="product_scd effective-end" propertyName="levelScdEffectiveEnd_product_scd" numFmtId="0" hierarchy="15" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20070630" maxValue="99991231" count="2">
+        <n v="20070630"/>
         <n v="99991231"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[levelScdEffectiveStart_product_scd]" caption="product_scd effective-start" propertyName="levelScdEffectiveStart_product_scd" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[levelScdEffectiveStart_product_scd]" caption="product_scd effective-start" propertyName="levelScdEffectiveStart_product_scd" numFmtId="0" hierarchy="15" level="1" memberPropertyField="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20060701" maxValue="20070701" count="2">
         <n v="20060701"/>
         <n v="20070701"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[product_scd_line]" caption="Product Line" propertyName="product_scd_line" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[product_scd_line]" caption="Product Line" propertyName="product_scd_line" numFmtId="0" hierarchy="15" level="1" memberPropertyField="1">
       <sharedItems count="1">
-        <s v="S "/>
+        <s v="M "/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[product_scd_list_price]" caption="List Price" propertyName="product_scd_list_price" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="33.644199371337891" maxValue="34.990001678466797" count="2">
-        <n v="33.644199371337891"/>
-        <n v="34.990001678466797"/>
+    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[product_scd_list_price]" caption="List Price" propertyName="product_scd_list_price" numFmtId="0" hierarchy="15" level="1" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2049.09814453125" maxValue="2294.989990234375" count="2">
+        <n v="2049.09814453125"/>
+        <n v="2294.989990234375"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[product_scd_subcategory]" caption="Product Subcategory" propertyName="product_scd_subcategory" numFmtId="0" hierarchy="12" level="1" memberPropertyField="1">
+    <cacheField name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].[product_scd_subcategory]" caption="Product Subcategory" propertyName="product_scd_subcategory" numFmtId="0" hierarchy="15" level="1" memberPropertyField="1">
       <sharedItems count="1">
-        <s v="S -31"/>
+        <s v="M -1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[levelScdEffectiveEnd_product_scd]" caption="product_scd effective-end" numFmtId="0" hierarchy="13" level="1">
+    <cacheField name="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[levelScdEffectiveEnd_product_scd]" caption="product_scd effective-end" numFmtId="0" hierarchy="16" level="1">
       <sharedItems count="2">
-        <s v="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[levelScdEffectiveEnd_product_scd].&amp;[20070701]" c="20070701"/>
+        <s v="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[levelScdEffectiveEnd_product_scd].&amp;[20070630]" c="20070630"/>
         <s v="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[levelScdEffectiveEnd_product_scd].&amp;[99991231]" c="99991231"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Product SCD Dimension].[levelScdEffectiveStart_product_scd].[levelScdEffectiveStart_product_scd]" caption="product_scd effective-start" numFmtId="0" hierarchy="14" level="1">
+    <cacheField name="[Product SCD Dimension].[levelScdEffectiveStart_product_scd].[levelScdEffectiveStart_product_scd]" caption="product_scd effective-start" numFmtId="0" hierarchy="17" level="1">
       <sharedItems count="2">
         <s v="[Product SCD Dimension].[levelScdEffectiveStart_product_scd].[levelScdEffectiveStart_product_scd].&amp;[20060701]" c="20060701"/>
         <s v="[Product SCD Dimension].[levelScdEffectiveStart_product_scd].[levelScdEffectiveStart_product_scd].&amp;[20070701]" c="20070701"/>
       </sharedItems>
     </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Year]" caption="ReportIng Year" numFmtId="0" hierarchy="10" level="1">
+      <sharedItems count="3">
+        <s v="[Date Dimension].[Retail445].[rpt_Year].&amp;[2006-01-01T00:00:00]" c="Reporting Calendar 2006"/>
+        <s v="[Date Dimension].[Retail445].[rpt_Year].&amp;[2007-01-07T00:00:00]" c="Reporting Calendar 2007"/>
+        <s v="[Date Dimension].[Retail445].[rpt_Year].&amp;[2008-01-06T00:00:00]" c="Reporting Calendar 2008"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Half_Year]" caption="ReportIng Half Year" numFmtId="0" hierarchy="10" level="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Quarter]" caption="ReportIng Quarter" numFmtId="0" hierarchy="10" level="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Month]" caption="ReportIng Month" numFmtId="0" hierarchy="10" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Week]" caption="ReportIng Week" numFmtId="0" hierarchy="10" level="5">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Day]" caption="Reporting Day" numFmtId="0" hierarchy="10" level="6">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Half_Year].[Reporting_Half_Year_Of_Year]" caption="ReportIng Half Year Of Year" propertyName="Reporting_Half_Year_Of_Year" numFmtId="0" hierarchy="10" level="2" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Quarter].[Reporting_Quarter_Of_Year]" caption="ReportIng Quarter Of Year" propertyName="Reporting_Quarter_Of_Year" numFmtId="0" hierarchy="10" level="3" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Month].[Reporting_Month_Of_Quarter]" caption="ReportIng Month Of Quarter" propertyName="Reporting_Month_Of_Quarter" numFmtId="0" hierarchy="10" level="4" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Month].[Reporting_Month_Of_Year]" caption="ReportIng Month Of Year" propertyName="Reporting_Month_Of_Year" numFmtId="0" hierarchy="10" level="4" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Month].[d_Reporting_Month_Name]" caption="ReportIng Month Name" propertyName="d_Reporting_Month_Name" numFmtId="0" hierarchy="10" level="4" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Week].[Reporting_Week_Of_Month]" caption="ReportIng Week Of Month" propertyName="Reporting_Week_Of_Month" numFmtId="0" hierarchy="10" level="5" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Week].[Reporting_Week_Of_Year]" caption="ReportIng Week Of Year" propertyName="Reporting_Week_Of_Year" numFmtId="0" hierarchy="10" level="5" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Day].[Reporting_Day_Of_Month]" caption="ReportIng Day Of Month" propertyName="Reporting_Day_Of_Month" numFmtId="0" hierarchy="10" level="6" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Day].[Reporting_Day_Of_Week]" caption="ReportIng Day Of Week" propertyName="Reporting_Day_Of_Week" numFmtId="0" hierarchy="10" level="6" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Date Dimension].[Retail445].[rpt_Day].[Reporting_Day_Of_Year]" caption="ReportIng Day Of Year" propertyName="Reporting_Day_Of_Year" numFmtId="0" hierarchy="10" level="6" memberPropertyField="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Product SCD Dimension].[product_scd_list_price].[product_scd_list_price]" caption="List Price" numFmtId="0" hierarchy="22" level="1">
+      <sharedItems count="2">
+        <s v="[Product SCD Dimension].[product_scd_list_price].[product_scd_list_price].&amp;[2049.0981]" c="2049.0981"/>
+        <s v="[Product SCD Dimension].[product_scd_list_price].[product_scd_list_price].&amp;[2294.99]" c="2294.99"/>
+      </sharedItems>
+    </cacheField>
   </cacheFields>
-  <cacheHierarchies count="27">
+  <cacheHierarchies count="30">
     <cacheHierarchy uniqueName="[Date Dimension].[Calculation Group Date Month]" caption="Calculation Group Date Month" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[Calculation Group Date Month].&amp;[Current]" dimensionUniqueName="[Date Dimension]" displayFolder="Calculated Groups" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Date Dimension].[Reporting_Day_Of_Month]" caption="ReportIng Day Of Month" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[Reporting_Day_Of_Month].[All]" allUniqueName="[Date Dimension].[Reporting_Day_Of_Month].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Date Dimension].[Reporting_Day_Of_Week]" caption="ReportIng Day Of Week" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[Reporting_Day_Of_Week].[All]" allUniqueName="[Date Dimension].[Reporting_Day_Of_Week].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
@@ -230,24 +287,37 @@
     <cacheHierarchy uniqueName="[Date Dimension].[Reporting_Quarter_Of_Year]" caption="ReportIng Quarter Of Year" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[Reporting_Quarter_Of_Year].[All]" allUniqueName="[Date Dimension].[Reporting_Quarter_Of_Year].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Date Dimension].[Reporting_Week_Of_Month]" caption="ReportIng Week Of Month" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[Reporting_Week_Of_Month].[All]" allUniqueName="[Date Dimension].[Reporting_Week_Of_Month].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Date Dimension].[Reporting_Week_Of_Year]" caption="ReportIng Week Of Year" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[Reporting_Week_Of_Year].[All]" allUniqueName="[Date Dimension].[Reporting_Week_Of_Year].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Date Dimension].[Retail445]" caption="Retail445" time="1" defaultMemberUniqueName="[Date Dimension].[Retail445].[All]" allUniqueName="[Date Dimension].[Retail445].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Date Dimension].[Retail445]" caption="Retail445" time="1" defaultMemberUniqueName="[Date Dimension].[Retail445].[All]" allUniqueName="[Date Dimension].[Retail445].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="7" unbalanced="0">
+      <fieldsUsage count="7">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="9"/>
+        <fieldUsage x="10"/>
+        <fieldUsage x="11"/>
+        <fieldUsage x="12"/>
+        <fieldUsage x="13"/>
+        <fieldUsage x="14"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Date Dimension].[d_Reporting_Month_Name]" caption="ReportIng Month Name" attribute="1" time="1" defaultMemberUniqueName="[Date Dimension].[d_Reporting_Month_Name].[All]" allUniqueName="[Date Dimension].[d_Reporting_Month_Name].[All]" dimensionUniqueName="[Date Dimension]" displayFolder="Date Attributes" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Order Dimension SCD].[Order Dimension SCD hierarchy]" caption="Order Dimension" defaultMemberUniqueName="[Order Dimension SCD].[Order Dimension SCD hierarchy].[All]" allUniqueName="[Order Dimension SCD].[Order Dimension SCD hierarchy].[All]" dimensionUniqueName="[Order Dimension SCD]" displayFolder="Orders" count="3" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Order Dimension SCD].[currency_scd]" caption="Currency" attribute="1" defaultMemberUniqueName="[Order Dimension SCD].[currency_scd].[All]" allUniqueName="[Order Dimension SCD].[currency_scd].[All]" dimensionUniqueName="[Order Dimension SCD]" displayFolder="Orders" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Order Dimension SCD].[typeorder_scd]" caption="Order Type" attribute="1" defaultMemberUniqueName="[Order Dimension SCD].[typeorder_scd].[All]" allUniqueName="[Order Dimension SCD].[typeorder_scd].[All]" dimensionUniqueName="[Order Dimension SCD]" displayFolder="Orders" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Product SCD Dimension].[Product SCD hierarchy]" caption="Product" time="1" defaultMemberUniqueName="[Product SCD Dimension].[Product SCD hierarchy].[All]" allUniqueName="[Product SCD Dimension].[Product SCD hierarchy].[All]" dimensionUniqueName="[Product SCD Dimension]" displayFolder="Products" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
+        <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd]" caption="product_scd effective-end" attribute="1" defaultMemberUniqueName="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[All]" allUniqueName="[Product SCD Dimension].[levelScdEffectiveEnd_product_scd].[All]" dimensionUniqueName="[Product SCD Dimension]" displayFolder="Products" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="8"/>
+        <fieldUsage x="7"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Product SCD Dimension].[levelScdEffectiveStart_product_scd]" caption="product_scd effective-start" attribute="1" defaultMemberUniqueName="[Product SCD Dimension].[levelScdEffectiveStart_product_scd].[All]" allUniqueName="[Product SCD Dimension].[levelScdEffectiveStart_product_scd].[All]" dimensionUniqueName="[Product SCD Dimension]" displayFolder="Products" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="9"/>
+        <fieldUsage x="8"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Product SCD Dimension].[product_scd As-Of-Date]" caption="product_scd As-Of-Date" attribute="1" time="1" keyAttribute="1" defaultMemberUniqueName="[Product SCD Dimension].[product_scd As-Of-Date].[All]" allUniqueName="[Product SCD Dimension].[product_scd As-Of-Date].[All]" dimensionUniqueName="[Product SCD Dimension]" displayFolder="Products" count="0" memberValueDatatype="7" unbalanced="0"/>
@@ -257,7 +327,7 @@
     <cacheHierarchy uniqueName="[Product SCD Dimension].[product_scd_list_price]" caption="List Price" attribute="1" defaultMemberUniqueName="[Product SCD Dimension].[product_scd_list_price].[All]" allUniqueName="[Product SCD Dimension].[product_scd_list_price].[All]" dimensionUniqueName="[Product SCD Dimension]" displayFolder="Products" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
+        <fieldUsage x="25"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Product SCD Dimension].[product_scd_subcategory]" caption="Product Subcategory" attribute="1" defaultMemberUniqueName="[Product SCD Dimension].[product_scd_subcategory].[All]" allUniqueName="[Product SCD Dimension].[product_scd_subcategory].[All]" dimensionUniqueName="[Product SCD Dimension]" displayFolder="Products" count="0" unbalanced="0"/>
@@ -273,19 +343,21 @@
     </cacheHierarchy>
   </cacheHierarchies>
   <kpis count="0"/>
-  <dimensions count="4">
+  <dimensions count="5">
     <dimension name="Date Dimension" uniqueName="[Date Dimension]" caption="Date Dimension"/>
     <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Order Dimension SCD" uniqueName="[Order Dimension SCD]" caption="Order Dimension SCD"/>
     <dimension name="Product SCD Dimension" uniqueName="[Product SCD Dimension]" caption="Product SCD Dimension"/>
     <dimension name="Version History" uniqueName="[Version History]" caption="Version History"/>
   </dimensions>
   <measureGroups count="1">
     <measureGroup name="Sales Product SCD" caption="Sales Product SCD"/>
   </measureGroups>
-  <maps count="3">
+  <maps count="4">
     <map measureGroup="0" dimension="0"/>
     <map measureGroup="0" dimension="2"/>
     <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
   </maps>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -296,55 +368,230 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C0147A9-4C16-41E1-837E-EFD3539B7DB6}" name="PivotTable4" cacheId="64" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A1:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="4"/>
-  <pivotFields count="10">
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB661A10-A363-46A2-BA3A-485F8B30C365}" name="PivotTable6" cacheId="203" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="B5:G10" firstHeaderRow="1" firstDataRow="1" firstDataCol="5"/>
+  <pivotFields count="26">
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="2">
         <item x="0"/>
         <item x="1"/>
       </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="2">
         <item x="0"/>
         <item x="1"/>
       </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="3">
+        <item c="1" x="0"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
     </pivotField>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="2">
         <item x="0"/>
         <item x="1"/>
       </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
     </pivotField>
   </pivotFields>
-  <rowFields count="4">
-    <field x="2"/>
+  <rowFields count="5">
     <field x="1"/>
+    <field x="8"/>
+    <field x="7"/>
     <field x="9"/>
-    <field x="8"/>
+    <field x="25"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="5">
     <i>
       <x/>
       <x/>
       <x/>
+      <x/>
+      <x/>
+    </i>
+    <i r="3">
+      <x v="1"/>
       <x/>
     </i>
     <i>
@@ -352,29 +599,10 @@
       <x v="1"/>
       <x v="1"/>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x/>
-      <x/>
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x v="1"/>
-      <x v="1"/>
       <x v="1"/>
     </i>
-    <i>
-      <x v="4"/>
-      <x/>
-      <x/>
-      <x/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="1"/>
-      <x v="1"/>
+    <i r="3">
+      <x v="2"/>
       <x v="1"/>
     </i>
     <i t="grand">
@@ -387,31 +615,45 @@
   <dataFields count="1">
     <dataField fld="0" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotHierarchies count="27">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
+  <pivotHierarchies count="30">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy>
+      <mps count="10">
+        <mp field="15"/>
+        <mp field="16"/>
+        <mp field="17"/>
+        <mp field="18"/>
+        <mp field="19"/>
+        <mp field="20"/>
+        <mp field="21"/>
+        <mp field="22"/>
+        <mp field="23"/>
+        <mp field="24"/>
+      </mps>
+    </pivotHierarchy>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy>
       <mps count="5">
+        <mp field="2"/>
         <mp field="3"/>
         <mp field="4"/>
         <mp field="5"/>
         <mp field="6"/>
-        <mp field="7"/>
       </mps>
-      <members count="3" level="1">
-        <member name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Red]"/>
-        <member name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Blue]"/>
-        <member name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Sport-100 Helmet, Black]"/>
+      <members count="1" level="1">
+        <member name="[Product SCD Dimension].[Product SCD hierarchy].[product_scd].&amp;[Mountain-200 Black, 46]"/>
       </members>
     </pivotHierarchy>
     <pivotHierarchy/>
@@ -430,15 +672,16 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="4">
-    <rowHierarchyUsage hierarchyUsage="12"/>
-    <rowHierarchyUsage hierarchyUsage="19"/>
-    <rowHierarchyUsage hierarchyUsage="14"/>
-    <rowHierarchyUsage hierarchyUsage="13"/>
+  <rowHierarchiesUsage count="5">
+    <rowHierarchyUsage hierarchyUsage="15"/>
+    <rowHierarchyUsage hierarchyUsage="17"/>
+    <rowHierarchyUsage hierarchyUsage="16"/>
+    <rowHierarchyUsage hierarchyUsage="10"/>
+    <rowHierarchyUsage hierarchyUsage="22"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" calculatedMembersInFilters="1" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
@@ -763,198 +1006,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A551FF-3E2B-4187-B08F-0308682DDD68}">
-  <dimension ref="A1:E8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3B104C-772E-4834-97DB-D51986F64303}">
+  <dimension ref="B5:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="41" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="47" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="51" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="56" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="61" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="67" max="71" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="72" max="79" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="80" max="84" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="85" max="98" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="99" max="110" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="111" max="122" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="123" max="126" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="29" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="131" max="132" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="133" max="134" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="135" max="136" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="139" max="142" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="143" max="146" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="147" max="155" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="156" max="160" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="42" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="48" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="52" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="57" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="62" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="72" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="73" max="80" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="81" max="85" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="86" max="99" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="100" max="111" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="112" max="123" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="124" max="127" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="29" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="132" max="133" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="134" max="135" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="136" max="137" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="140" max="143" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="144" max="147" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="148" max="156" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="157" max="161" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>290972.21875</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>393427.21875</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>761936.6875</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1">
-        <v>34.990001678466797</v>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>794066.5625</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1">
-        <v>118056.265625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1">
-        <v>34.990001678466797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1">
-        <v>116271.7734375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1">
-        <v>104.97000122070313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1">
-        <v>121275.34375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="1">
-        <v>355778.34375</v>
+      <c r="G10" s="1">
+        <v>2240402.75</v>
       </c>
     </row>
   </sheetData>
